--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,7 +3033,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46165.35750949529</v>
+        <v>46165.35750949074</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46165.357519812</v>
+        <v>46165.35751981482</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46165.36053373099</v>
+        <v>46165.36053372685</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46165.36378095004</v>
+        <v>46165.36378094908</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46165.36458809603</v>
+        <v>46165.36458809028</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46165.36560757287</v>
+        <v>46165.36560756945</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46165.36607571008</v>
+        <v>46165.36607570602</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46165.36907937931</v>
+        <v>46165.369079375</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46165.3691080567</v>
+        <v>46165.36910805556</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46165.36921845662</v>
+        <v>46165.36921846065</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46165.36923027316</v>
+        <v>46165.36923027778</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46165.36923741666</v>
+        <v>46165.36923741898</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46165.36924354335</v>
+        <v>46165.36924354167</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46165.36924930302</v>
+        <v>46165.36924930556</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -3296,6 +3296,272 @@
         <v>0.5</v>
       </c>
       <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46166.23453480066</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46166.23453785618</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46166.23626762178</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>149.45</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46166.2380037841</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>150</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46166.23834853512</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46166.23866386646</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46166.23882926233</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46166.24014366619</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>113.56</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46166.24015341029</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46166.24017151437</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46166.2401749779</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46166.24017651539</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46166.24017791354</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46166.24017940005</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3299,7 +3299,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46166.23453480066</v>
+        <v>46166.23453480324</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46166.23453785618</v>
+        <v>46166.2345378588</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46166.23626762178</v>
+        <v>46166.23626762731</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46166.2380037841</v>
+        <v>46166.23800378473</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46166.23834853512</v>
+        <v>46166.2383485301</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46166.23866386646</v>
+        <v>46166.23866386574</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46166.23882926233</v>
+        <v>46166.23882925926</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46166.24014366619</v>
+        <v>46166.24014366898</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46166.24015341029</v>
+        <v>46166.24015341435</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46166.24017151437</v>
+        <v>46166.24017151621</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46166.2401749779</v>
+        <v>46166.24017497685</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46166.24017651539</v>
+        <v>46166.24017651621</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46166.24017791354</v>
+        <v>46166.24017791667</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46166.24017940005</v>
+        <v>46166.24017939815</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3562,6 +3562,272 @@
         <v>0.13</v>
       </c>
       <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46167.60763489008</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46167.60763668691</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46167.60922294667</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46167.61106374522</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>159.04</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46167.61142138461</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46167.6117345793</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46167.61190646449</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46167.61324575615</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>115.71</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46167.61325279409</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46167.61327033606</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46167.61327056596</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46167.61327067688</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46167.61327195516</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46167.61327215927</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,7 +3565,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46167.60763489008</v>
+        <v>46167.60763489583</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46167.60763668691</v>
+        <v>46167.60763668981</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46167.60922294667</v>
+        <v>46167.60922295139</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46167.61106374522</v>
+        <v>46167.61106375</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46167.61142138461</v>
+        <v>46167.61142138889</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46167.6117345793</v>
+        <v>46167.61173458333</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46167.61190646449</v>
+        <v>46167.61190646991</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46167.61324575615</v>
+        <v>46167.61324575231</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46167.61325279409</v>
+        <v>46167.61325278935</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46167.61327033606</v>
+        <v>46167.61327033565</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46167.61327056596</v>
+        <v>46167.61327056713</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46167.61327067688</v>
+        <v>46167.6132706713</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46167.61327195516</v>
+        <v>46167.61327195602</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46167.61327215927</v>
+        <v>46167.61327216435</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3828,6 +3828,272 @@
         <v>0.02</v>
       </c>
       <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46168.60016924667</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46168.60016986766</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168.60166993549</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46168.60331316395</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>141.97</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46168.60363531478</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46168.60393747274</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46168.60410251324</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46168.60530711792</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>104.08</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46168.60531259455</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46168.60533155398</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46168.60533175628</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46168.60533184956</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46168.60533302488</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46168.6053332128</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3831,7 +3831,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168.60016924667</v>
+        <v>46168.60016924769</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46168.60016986766</v>
+        <v>46168.60016987268</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168.60166993549</v>
+        <v>46168.60166993055</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46168.60331316395</v>
+        <v>46168.60331315972</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46168.60363531478</v>
+        <v>46168.6036353125</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46168.60393747274</v>
+        <v>46168.60393747685</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46168.60410251324</v>
+        <v>46168.60410251158</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46168.60530711792</v>
+        <v>46168.60530711806</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46168.60531259455</v>
+        <v>46168.60531259259</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46168.60533155398</v>
+        <v>46168.60533155093</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46168.60533175628</v>
+        <v>46168.60533175926</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46168.60533184956</v>
+        <v>46168.60533185185</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46168.60533302488</v>
+        <v>46168.60533302083</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46168.6053332128</v>
+        <v>46168.60533321759</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -4094,6 +4094,272 @@
         <v>0.02</v>
       </c>
       <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46169.62440551414</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46169.62440613694</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46169.62599742919</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46169.62779027034</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46169.62814372868</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46169.62845739415</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46169.62862731211</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46169.62995702927</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>114.89</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46169.62996736027</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46169.62998345323</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46169.629983668</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46169.62998377231</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46169.6299849908</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46169.62998519091</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4097,7 +4097,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46169.62440551414</v>
+        <v>46169.62440550926</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46169.62440613694</v>
+        <v>46169.62440613426</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46169.62599742919</v>
+        <v>46169.62599743056</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46169.62779027034</v>
+        <v>46169.6277902662</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46169.62814372868</v>
+        <v>46169.62814372686</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46169.62845739415</v>
+        <v>46169.62845739583</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46169.62862731211</v>
+        <v>46169.62862731481</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46169.62995702927</v>
+        <v>46169.62995702546</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46169.62996736027</v>
+        <v>46169.62996736111</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46169.62998345323</v>
+        <v>46169.62998344907</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46169.629983668</v>
+        <v>46169.62998366898</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46169.62998377231</v>
+        <v>46169.62998377315</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46169.6299849908</v>
+        <v>46169.62998498842</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46169.62998519091</v>
+        <v>46169.62998518519</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -4360,6 +4360,272 @@
         <v>0.02</v>
       </c>
       <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46170.37165898731</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46170.37165957863</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46170.37326877123</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>139.03</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46170.37488347518</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>139.51</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46170.37522005743</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46170.37552707317</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46170.37569246176</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46170.37695467904</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>109.06</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46170.37695984996</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46170.37697993378</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46170.37698015009</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46170.37698025591</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46170.37698162611</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46170.37698185258</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4363,7 +4363,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46170.37165898731</v>
+        <v>46170.37165899306</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46170.37165957863</v>
+        <v>46170.37165958333</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46170.37326877123</v>
+        <v>46170.37326877315</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46170.37488347518</v>
+        <v>46170.37488347222</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46170.37522005743</v>
+        <v>46170.37522005787</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46170.37552707317</v>
+        <v>46170.37552707176</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46170.37569246176</v>
+        <v>46170.37569246528</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46170.37695467904</v>
+        <v>46170.37695467593</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46170.37695984996</v>
+        <v>46170.37695984953</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46170.37697993378</v>
+        <v>46170.37697993056</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46170.37698015009</v>
+        <v>46170.37698015046</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46170.37698025591</v>
+        <v>46170.37698025463</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46170.37698162611</v>
+        <v>46170.37698162037</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46170.37698185258</v>
+        <v>46170.37698185185</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4626,6 +4626,272 @@
         <v>0.02</v>
       </c>
       <c r="E221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46170.72452332536</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46170.72452398463</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46170.72609570251</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46170.72786794355</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46170.7282128617</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46170.72852569856</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46170.72869176725</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46170.73000041371</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>113.07</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46170.73001053976</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46170.73002288597</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46170.73002310074</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46170.73002320001</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46170.73002439665</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46170.73002459254</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/football/logs/daily_football_cycle_log.xlsx
+++ b/data/football/logs/daily_football_cycle_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4629,7 +4629,7 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46170.72452332536</v>
+        <v>46170.72452332176</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46170.72452398463</v>
+        <v>46170.72452398148</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46170.72609570251</v>
+        <v>46170.72609570602</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46170.72786794355</v>
+        <v>46170.72786793982</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46170.7282128617</v>
+        <v>46170.7282128588</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46170.72852569856</v>
+        <v>46170.72852569445</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46170.72869176725</v>
+        <v>46170.72869177083</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46170.73000041371</v>
+        <v>46170.73000041667</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46170.73001053976</v>
+        <v>46170.73001054398</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46170.73002288597</v>
+        <v>46170.73002288194</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46170.73002310074</v>
+        <v>46170.73002310185</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46170.73002320001</v>
+        <v>46170.73002319445</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46170.73002439665</v>
+        <v>46170.73002439815</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46170.73002459254</v>
+        <v>46170.73002459491</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4892,6 +4892,272 @@
         <v>0.02</v>
       </c>
       <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46170.82684172941</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Backtest Previous Fixture Predictions</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46170.82684233767</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Cleanup Past Fixtures</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46170.82843009164</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Build Football Master Dataset</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>137.18</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46170.83005822739</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Build Football Features</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>140.67</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46170.8304039959</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Goals Model</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46170.83072812993</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Result Model</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46170.83090819464</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Corners Model</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46170.83217858186</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Historical Ensemble Engine</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46170.83218360694</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Build Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46170.83220200033</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Predict Football Fixtures</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46170.83220221219</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Archive Daily Predictions</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46170.83220231334</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Football Value Bet Engine</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46170.83220362005</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Football Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46170.83220381958</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Top Plays Report</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
